--- a/KR_Comparison.xlsx
+++ b/KR_Comparison.xlsx
@@ -60,11 +60,11 @@
   </si>
   <si>
     <t>Exp
-FBOPN</t>
+FBOPN_EN</t>
   </si>
   <si>
     <t>Exp
-FBCLS</t>
+FBCLS_EN</t>
   </si>
   <si>
     <t>DB
@@ -84,11 +84,11 @@
   </si>
   <si>
     <t>DB
-FBOPN</t>
+FBOPN_EN</t>
   </si>
   <si>
     <t>DB
-FBCLS</t>
+FBCLS_EN</t>
   </si>
   <si>
     <t>Match</t>
@@ -112,52 +112,52 @@
     <t>X</t>
   </si>
   <si>
+    <t>NC</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>OK</t>
+  </si>
+  <si>
+    <t>AV208-1</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>EM - 208</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>DIFF</t>
+  </si>
+  <si>
+    <t>UPDATE: VLV_W_FB: DB=True-&gt;False, FB_OPN_EN: DB=True-&gt;False, FB_CLS_EN: DB=True-&gt;False</t>
+  </si>
+  <si>
+    <t>AV210-1</t>
+  </si>
+  <si>
+    <t>EM - 210</t>
+  </si>
+  <si>
+    <t>UPDATE: EXIST: DB=True-&gt;False, VLV_W_FB: DB=True-&gt;False, FB_OPN_EN: DB=True-&gt;False, FB_CLS_EN: DB=True-&gt;False</t>
+  </si>
+  <si>
+    <t>AV212-1</t>
+  </si>
+  <si>
+    <t>EM - 212</t>
+  </si>
+  <si>
     <t>NO</t>
-  </si>
-  <si>
-    <t>T</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>OK</t>
-  </si>
-  <si>
-    <t>AV208-1</t>
-  </si>
-  <si>
-    <t>Unknown</t>
-  </si>
-  <si>
-    <t>EM - 208</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>DIFF</t>
-  </si>
-  <si>
-    <t>UPDATE: VLV_W_FB: DB=True-&gt;False, FB_OPN_EN: DB=True-&gt;False, FB_CLS_EN: DB=True-&gt;False</t>
-  </si>
-  <si>
-    <t>AV210-1</t>
-  </si>
-  <si>
-    <t>EM - 210</t>
-  </si>
-  <si>
-    <t>UPDATE: EXIST: DB=True-&gt;False, VLV_W_FB: DB=True-&gt;False, FB_OPN_EN: DB=True-&gt;False, FB_CLS_EN: DB=True-&gt;False</t>
-  </si>
-  <si>
-    <t>AV212-1</t>
-  </si>
-  <si>
-    <t>EM - 212</t>
-  </si>
-  <si>
-    <t>NC</t>
   </si>
   <si>
     <t>UPDATE: ENABLE: DB=True-&gt;False, EXIST: DB=True-&gt;False, VLV_W_FB: DB=True-&gt;False, FB_OPN_EN: DB=True-&gt;False, FB_CLS_EN: DB=True-&gt;False</t>

--- a/KR_Comparison.xlsx
+++ b/KR_Comparison.xlsx
@@ -127,7 +127,7 @@
     <t>AV208-1</t>
   </si>
   <si>
-    <t>Unknown</t>
+    <t>Options</t>
   </si>
   <si>
     <t>EM - 208</t>
@@ -211,6 +211,9 @@
     <t>AV460d-1</t>
   </si>
   <si>
+    <t>Unit Sep</t>
+  </si>
+  <si>
     <t>EM - 460</t>
   </si>
   <si>
@@ -244,9 +247,6 @@
     <t>COOLING LIQUID FLOW</t>
   </si>
   <si>
-    <t>Unit Sep</t>
-  </si>
-  <si>
     <t>EM - 400</t>
   </si>
   <si>
@@ -319,99 +319,102 @@
     <t>eWON Talk2M STATUS</t>
   </si>
   <si>
+    <t>UPDATE: ENABLE: DB=False-&gt;True, EXIST: DB=False-&gt;True</t>
+  </si>
+  <si>
+    <t>LA201-1</t>
+  </si>
+  <si>
+    <t>INLET SIGHT GLASS BACKLIGHT</t>
+  </si>
+  <si>
+    <t>UPDATE: ENABLE: DB=True-&gt;False, EXIST: DB=True-&gt;False</t>
+  </si>
+  <si>
+    <t>LA220-1</t>
+  </si>
+  <si>
+    <t>OUTLET SIGHT GLASS BACKLIGHT</t>
+  </si>
+  <si>
+    <t>L-GREEN</t>
+  </si>
+  <si>
+    <t>SIGNAL TOWER-GREEN LIGHT</t>
+  </si>
+  <si>
+    <t>L-YELLOW</t>
+  </si>
+  <si>
+    <t>SIGNAL TOWER-YELLOW LIGHT</t>
+  </si>
+  <si>
+    <t>L-RED</t>
+  </si>
+  <si>
+    <t>SIGNAL TOWER-RED LIGHT/ALARM LIGHT</t>
+  </si>
+  <si>
+    <t>L-BUZZ</t>
+  </si>
+  <si>
+    <t>SIGNAL TOWER-BUZZIER</t>
+  </si>
+  <si>
+    <t>LA221-1</t>
+  </si>
+  <si>
+    <t>PIT201-1</t>
+  </si>
+  <si>
+    <t>INLET PRESSURE</t>
+  </si>
+  <si>
+    <t>PIT22X-1</t>
+  </si>
+  <si>
+    <t>SEPARATOR OUTLET 220 PRESSURE</t>
+  </si>
+  <si>
+    <t>QT201-1</t>
+  </si>
+  <si>
+    <t>INLET TURBIDITY</t>
+  </si>
+  <si>
+    <t>QT220-1</t>
+  </si>
+  <si>
+    <t>OUTLET TURBIDITY</t>
+  </si>
+  <si>
+    <t>QT220-2</t>
+  </si>
+  <si>
+    <t>PIT22Y-1</t>
+  </si>
+  <si>
+    <t>SEPARATOR OUTLET 221 PRESSURE</t>
+  </si>
+  <si>
+    <t>PIT222-1</t>
+  </si>
+  <si>
+    <t>SOLIDS OUTLET PRESSURE</t>
+  </si>
+  <si>
+    <t>LT-BT</t>
+  </si>
+  <si>
+    <t>BUFFER TANK LEVEL</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
     <t>N/F</t>
   </si>
   <si>
-    <t>LA201-1</t>
-  </si>
-  <si>
-    <t>INLET SIGHT GLASS BACKLIGHT</t>
-  </si>
-  <si>
-    <t>UPDATE: ENABLE: DB=True-&gt;False, EXIST: DB=True-&gt;False</t>
-  </si>
-  <si>
-    <t>LA220-1</t>
-  </si>
-  <si>
-    <t>OUTLET SIGHT GLASS BACKLIGHT</t>
-  </si>
-  <si>
-    <t>L-GREEN</t>
-  </si>
-  <si>
-    <t>SIGNAL TOWER-GREEN LIGHT</t>
-  </si>
-  <si>
-    <t>L-YELLOW</t>
-  </si>
-  <si>
-    <t>SIGNAL TOWER-YELLOW LIGHT</t>
-  </si>
-  <si>
-    <t>L-RED</t>
-  </si>
-  <si>
-    <t>SIGNAL TOWER-RED LIGHT/ALARM LIGHT</t>
-  </si>
-  <si>
-    <t>L-BUZZ</t>
-  </si>
-  <si>
-    <t>SIGNAL TOWER-BUZZIER</t>
-  </si>
-  <si>
-    <t>LA221-1</t>
-  </si>
-  <si>
-    <t>PIT201-1</t>
-  </si>
-  <si>
-    <t>INLET PRESSURE</t>
-  </si>
-  <si>
-    <t>PIT22X-1</t>
-  </si>
-  <si>
-    <t>SEPARATOR OUTLET 220 PRESSURE</t>
-  </si>
-  <si>
-    <t>QT201-1</t>
-  </si>
-  <si>
-    <t>INLET TURBIDITY</t>
-  </si>
-  <si>
-    <t>QT220-1</t>
-  </si>
-  <si>
-    <t>OUTLET TURBIDITY</t>
-  </si>
-  <si>
-    <t>QT220-2</t>
-  </si>
-  <si>
-    <t>PIT22Y-1</t>
-  </si>
-  <si>
-    <t>SEPARATOR OUTLET 221 PRESSURE</t>
-  </si>
-  <si>
-    <t>PIT222-1</t>
-  </si>
-  <si>
-    <t>SOLIDS OUTLET PRESSURE</t>
-  </si>
-  <si>
-    <t>LT-BT</t>
-  </si>
-  <si>
-    <t>BUFFER TANK LEVEL</t>
-  </si>
-  <si>
-    <t>O</t>
-  </si>
-  <si>
     <t>LT463-1</t>
   </si>
   <si>
@@ -610,9 +613,6 @@
     <t>FEED PUMP RUN FB</t>
   </si>
   <si>
-    <t>Options</t>
-  </si>
-  <si>
     <t>EM - P201</t>
   </si>
   <si>
@@ -649,13 +649,13 @@
     <t>FIS412-1</t>
   </si>
   <si>
-    <t>FS421A</t>
+    <t>FS421a</t>
   </si>
   <si>
     <t>LUB OIL FLOW TOP BEARING</t>
   </si>
   <si>
-    <t>FS421B</t>
+    <t>FS421b</t>
   </si>
   <si>
     <t>LUB OIL FLOW BOTTOM BEARING</t>
@@ -1813,7 +1813,7 @@
         <v>23</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>47</v>
@@ -2309,10 +2309,10 @@
         <v>23</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>34</v>
@@ -2365,7 +2365,7 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>23</v>
@@ -2374,7 +2374,7 @@
         <v>49</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>34</v>
@@ -2427,7 +2427,7 @@
     </row>
     <row r="19" spans="1:20">
       <c r="A19" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>23</v>
@@ -2436,7 +2436,7 @@
         <v>32</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>34</v>
@@ -2489,7 +2489,7 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>23</v>
@@ -2498,7 +2498,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>34</v>
@@ -2551,13 +2551,13 @@
     </row>
     <row r="21" spans="1:20">
       <c r="A21" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>47</v>
@@ -2619,10 +2619,10 @@
         <v>3</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>34</v>
@@ -2637,16 +2637,16 @@
         <v>29</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M22" s="4" t="s">
         <v>29</v>
@@ -2655,33 +2655,33 @@
         <v>29</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P22" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S22" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T22" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:20">
       <c r="A23" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>72</v>
@@ -2699,16 +2699,16 @@
         <v>28</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M23" s="5" t="s">
         <v>28</v>
@@ -2717,16 +2717,16 @@
         <v>28</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P23" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S23" s="5" t="s">
         <v>30</v>
@@ -2743,7 +2743,7 @@
         <v>74</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D24" s="4" t="s">
         <v>75</v>
@@ -2761,16 +2761,16 @@
         <v>29</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M24" s="4" t="s">
         <v>29</v>
@@ -2779,16 +2779,16 @@
         <v>28</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P24" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R24" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>35</v>
@@ -2805,7 +2805,7 @@
         <v>78</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>75</v>
@@ -2823,16 +2823,16 @@
         <v>29</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M25" s="4" t="s">
         <v>29</v>
@@ -2841,16 +2841,16 @@
         <v>28</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P25" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R25" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>35</v>
@@ -2867,7 +2867,7 @@
         <v>78</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D26" s="4" t="s">
         <v>75</v>
@@ -2885,16 +2885,16 @@
         <v>29</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J26" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M26" s="4" t="s">
         <v>29</v>
@@ -2903,16 +2903,16 @@
         <v>28</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P26" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R26" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>35</v>
@@ -2947,16 +2947,16 @@
         <v>28</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J27" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M27" s="4" t="s">
         <v>29</v>
@@ -2965,16 +2965,16 @@
         <v>28</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P27" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R27" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S27" s="6" t="s">
         <v>35</v>
@@ -3009,16 +3009,16 @@
         <v>28</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M28" s="5" t="s">
         <v>28</v>
@@ -3027,16 +3027,16 @@
         <v>28</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P28" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R28" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S28" s="5" t="s">
         <v>30</v>
@@ -3053,7 +3053,7 @@
         <v>87</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>88</v>
@@ -3071,16 +3071,16 @@
         <v>28</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M29" s="5" t="s">
         <v>28</v>
@@ -3089,16 +3089,16 @@
         <v>28</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P29" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q29" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R29" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S29" s="5" t="s">
         <v>30</v>
@@ -3133,16 +3133,16 @@
         <v>29</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J30" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M30" s="4" t="s">
         <v>29</v>
@@ -3151,16 +3151,16 @@
         <v>29</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P30" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R30" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S30" s="5" t="s">
         <v>30</v>
@@ -3195,16 +3195,16 @@
         <v>29</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M31" s="4" t="s">
         <v>29</v>
@@ -3213,16 +3213,16 @@
         <v>28</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P31" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>35</v>
@@ -3257,16 +3257,16 @@
         <v>29</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M32" s="4" t="s">
         <v>29</v>
@@ -3275,16 +3275,16 @@
         <v>29</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P32" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S32" s="5" t="s">
         <v>30</v>
@@ -3301,10 +3301,10 @@
         <v>95</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>26</v>
@@ -3319,16 +3319,16 @@
         <v>28</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J33" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M33" s="4" t="s">
         <v>29</v>
@@ -3337,22 +3337,22 @@
         <v>29</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P33" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q33" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R33" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="S33" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="S33" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="T33" s="6" t="s">
         <v>96</v>
-      </c>
-      <c r="T33" s="7" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:20">
@@ -3381,16 +3381,16 @@
         <v>29</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J34" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M34" s="5" t="s">
         <v>28</v>
@@ -3399,16 +3399,16 @@
         <v>28</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P34" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S34" s="6" t="s">
         <v>35</v>
@@ -3443,16 +3443,16 @@
         <v>28</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J35" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M35" s="5" t="s">
         <v>28</v>
@@ -3461,16 +3461,16 @@
         <v>28</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P35" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S35" s="5" t="s">
         <v>30</v>
@@ -3487,7 +3487,7 @@
         <v>103</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D36" s="4" t="s">
         <v>88</v>
@@ -3505,16 +3505,16 @@
         <v>28</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M36" s="4" t="s">
         <v>29</v>
@@ -3523,16 +3523,16 @@
         <v>28</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P36" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q36" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R36" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>35</v>
@@ -3549,7 +3549,7 @@
         <v>105</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>88</v>
@@ -3567,16 +3567,16 @@
         <v>29</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J37" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M37" s="4" t="s">
         <v>29</v>
@@ -3585,16 +3585,16 @@
         <v>28</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P37" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q37" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R37" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>35</v>
@@ -3611,7 +3611,7 @@
         <v>107</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D38" s="4" t="s">
         <v>88</v>
@@ -3629,16 +3629,16 @@
         <v>28</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J38" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M38" s="5" t="s">
         <v>28</v>
@@ -3647,16 +3647,16 @@
         <v>28</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P38" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q38" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R38" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S38" s="5" t="s">
         <v>30</v>
@@ -3673,7 +3673,7 @@
         <v>109</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>88</v>
@@ -3691,16 +3691,16 @@
         <v>28</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J39" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M39" s="5" t="s">
         <v>28</v>
@@ -3709,16 +3709,16 @@
         <v>28</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P39" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q39" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S39" s="5" t="s">
         <v>30</v>
@@ -3735,7 +3735,7 @@
         <v>101</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D40" s="4" t="s">
         <v>47</v>
@@ -3753,16 +3753,16 @@
         <v>29</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J40" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M40" s="4" t="s">
         <v>29</v>
@@ -3771,16 +3771,16 @@
         <v>28</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P40" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S40" s="6" t="s">
         <v>35</v>
@@ -3815,16 +3815,16 @@
         <v>28</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J41" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M41" s="5" t="s">
         <v>28</v>
@@ -3833,16 +3833,16 @@
         <v>28</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P41" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R41" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S41" s="5" t="s">
         <v>30</v>
@@ -3877,16 +3877,16 @@
         <v>28</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J42" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M42" s="5" t="s">
         <v>28</v>
@@ -3895,16 +3895,16 @@
         <v>28</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P42" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R42" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S42" s="5" t="s">
         <v>30</v>
@@ -3939,16 +3939,16 @@
         <v>29</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J43" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M43" s="4" t="s">
         <v>29</v>
@@ -3957,16 +3957,16 @@
         <v>29</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P43" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R43" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S43" s="5" t="s">
         <v>30</v>
@@ -4001,16 +4001,16 @@
         <v>29</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J44" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M44" s="4" t="s">
         <v>29</v>
@@ -4019,16 +4019,16 @@
         <v>28</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P44" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R44" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S44" s="6" t="s">
         <v>35</v>
@@ -4063,16 +4063,16 @@
         <v>29</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J45" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M45" s="4" t="s">
         <v>29</v>
@@ -4081,16 +4081,16 @@
         <v>29</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P45" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R45" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S45" s="5" t="s">
         <v>30</v>
@@ -4107,7 +4107,7 @@
         <v>121</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>47</v>
@@ -4125,16 +4125,16 @@
         <v>29</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J46" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M46" s="4" t="s">
         <v>29</v>
@@ -4143,16 +4143,16 @@
         <v>28</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P46" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R46" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S46" s="6" t="s">
         <v>35</v>
@@ -4187,16 +4187,16 @@
         <v>29</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J47" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M47" s="4" t="s">
         <v>29</v>
@@ -4205,16 +4205,16 @@
         <v>29</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P47" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R47" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S47" s="5" t="s">
         <v>30</v>
@@ -4231,10 +4231,10 @@
         <v>125</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>126</v>
@@ -4249,16 +4249,16 @@
         <v>29</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J48" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M48" s="4" t="s">
         <v>29</v>
@@ -4267,36 +4267,36 @@
         <v>29</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P48" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R48" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S48" s="7" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="T48" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" spans="1:20">
       <c r="A49" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>34</v>
@@ -4311,16 +4311,16 @@
         <v>29</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J49" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M49" s="4" t="s">
         <v>29</v>
@@ -4329,16 +4329,16 @@
         <v>29</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P49" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R49" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S49" s="5" t="s">
         <v>30</v>
@@ -4349,16 +4349,16 @@
     </row>
     <row r="50" spans="1:20">
       <c r="A50" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>34</v>
@@ -4373,16 +4373,16 @@
         <v>29</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J50" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M50" s="4" t="s">
         <v>29</v>
@@ -4391,16 +4391,16 @@
         <v>29</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P50" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R50" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S50" s="5" t="s">
         <v>30</v>
@@ -4411,16 +4411,16 @@
     </row>
     <row r="51" spans="1:20">
       <c r="A51" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>34</v>
@@ -4435,16 +4435,16 @@
         <v>29</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J51" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M51" s="4" t="s">
         <v>29</v>
@@ -4453,16 +4453,16 @@
         <v>29</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P51" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q51" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R51" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S51" s="5" t="s">
         <v>30</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="52" spans="1:20">
       <c r="A52" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>24</v>
@@ -4497,16 +4497,16 @@
         <v>28</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J52" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M52" s="5" t="s">
         <v>28</v>
@@ -4515,16 +4515,16 @@
         <v>28</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P52" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q52" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R52" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S52" s="5" t="s">
         <v>30</v>
@@ -4535,10 +4535,10 @@
     </row>
     <row r="53" spans="1:20">
       <c r="A53" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>32</v>
@@ -4559,16 +4559,16 @@
         <v>29</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J53" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M53" s="4" t="s">
         <v>29</v>
@@ -4577,16 +4577,16 @@
         <v>29</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P53" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R53" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S53" s="5" t="s">
         <v>30</v>
@@ -4597,13 +4597,13 @@
     </row>
     <row r="54" spans="1:20">
       <c r="A54" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>72</v>
@@ -4621,16 +4621,16 @@
         <v>28</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J54" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M54" s="5" t="s">
         <v>28</v>
@@ -4639,16 +4639,16 @@
         <v>28</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P54" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R54" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S54" s="5" t="s">
         <v>30</v>
@@ -4659,10 +4659,10 @@
     </row>
     <row r="55" spans="1:20">
       <c r="A55" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>24</v>
@@ -4683,16 +4683,16 @@
         <v>29</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J55" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M55" s="5" t="s">
         <v>28</v>
@@ -4701,16 +4701,16 @@
         <v>28</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P55" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q55" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R55" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S55" s="6" t="s">
         <v>35</v>
@@ -4721,10 +4721,10 @@
     </row>
     <row r="56" spans="1:20">
       <c r="A56" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>24</v>
@@ -4745,16 +4745,16 @@
         <v>28</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J56" s="4" t="s">
         <v>28</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M56" s="5" t="s">
         <v>28</v>
@@ -4763,36 +4763,36 @@
         <v>28</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P56" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q56" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R56" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S56" s="6" t="s">
         <v>35</v>
       </c>
       <c r="T56" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E57" s="5" t="s">
         <v>26</v>
@@ -4807,51 +4807,51 @@
         <v>28</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J57" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M57" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="N57" s="4" t="s">
-        <v>29</v>
+        <v>68</v>
+      </c>
+      <c r="M57" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="N57" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P57" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q57" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R57" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="S57" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="T57" s="7" t="s">
-        <v>68</v>
+        <v>68</v>
+      </c>
+      <c r="S57" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="T57" s="5" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>47</v>
@@ -4869,16 +4869,16 @@
         <v>29</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J58" s="4" t="s">
         <v>28</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M58" s="4" t="s">
         <v>29</v>
@@ -4887,16 +4887,16 @@
         <v>28</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P58" s="4" t="s">
         <v>28</v>
       </c>
       <c r="Q58" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R58" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>35</v>
@@ -4907,10 +4907,10 @@
     </row>
     <row r="59" spans="1:20">
       <c r="A59" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>32</v>
@@ -4931,16 +4931,16 @@
         <v>29</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J59" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M59" s="4" t="s">
         <v>29</v>
@@ -4949,16 +4949,16 @@
         <v>29</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P59" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q59" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R59" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S59" s="5" t="s">
         <v>30</v>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="60" spans="1:20">
       <c r="A60" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>32</v>
@@ -4993,16 +4993,16 @@
         <v>29</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J60" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M60" s="4" t="s">
         <v>29</v>
@@ -5011,16 +5011,16 @@
         <v>29</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P60" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q60" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R60" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S60" s="5" t="s">
         <v>30</v>
@@ -5031,16 +5031,16 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>34</v>
@@ -5055,16 +5055,16 @@
         <v>29</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J61" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M61" s="4" t="s">
         <v>29</v>
@@ -5073,16 +5073,16 @@
         <v>29</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P61" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R61" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S61" s="5" t="s">
         <v>30</v>
@@ -5093,13 +5093,13 @@
     </row>
     <row r="62" spans="1:20">
       <c r="A62" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>72</v>
@@ -5117,16 +5117,16 @@
         <v>28</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J62" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M62" s="5" t="s">
         <v>28</v>
@@ -5135,16 +5135,16 @@
         <v>28</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P62" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q62" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R62" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S62" s="5" t="s">
         <v>30</v>
@@ -5155,16 +5155,16 @@
     </row>
     <row r="63" spans="1:20">
       <c r="A63" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>26</v>
@@ -5179,16 +5179,16 @@
         <v>28</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J63" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>29</v>
@@ -5197,36 +5197,36 @@
         <v>29</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P63" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q63" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R63" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S63" s="7" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="T63" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="64" spans="1:20">
       <c r="A64" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>34</v>
@@ -5241,16 +5241,16 @@
         <v>29</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J64" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M64" s="4" t="s">
         <v>29</v>
@@ -5259,33 +5259,33 @@
         <v>29</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P64" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q64" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R64" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S64" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T64" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="65" spans="1:20">
       <c r="A65" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>88</v>
@@ -5303,16 +5303,16 @@
         <v>28</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J65" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M65" s="5" t="s">
         <v>28</v>
@@ -5321,16 +5321,16 @@
         <v>28</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P65" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q65" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R65" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S65" s="5" t="s">
         <v>30</v>
@@ -5341,13 +5341,13 @@
     </row>
     <row r="66" spans="1:20">
       <c r="A66" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D66" s="4" t="s">
         <v>88</v>
@@ -5365,16 +5365,16 @@
         <v>28</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J66" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M66" s="5" t="s">
         <v>28</v>
@@ -5383,36 +5383,36 @@
         <v>29</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P66" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q66" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R66" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S66" s="6" t="s">
         <v>35</v>
       </c>
       <c r="T66" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E67" s="5" t="s">
         <v>26</v>
@@ -5427,16 +5427,16 @@
         <v>28</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J67" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M67" s="5" t="s">
         <v>28</v>
@@ -5445,16 +5445,16 @@
         <v>28</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P67" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q67" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R67" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S67" s="5" t="s">
         <v>30</v>
@@ -5465,16 +5465,16 @@
     </row>
     <row r="68" spans="1:20">
       <c r="A68" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="E68" s="5" t="s">
         <v>26</v>
@@ -5489,16 +5489,16 @@
         <v>28</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J68" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M68" s="5" t="s">
         <v>28</v>
@@ -5507,16 +5507,16 @@
         <v>28</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P68" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q68" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R68" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S68" s="5" t="s">
         <v>30</v>
@@ -5527,10 +5527,10 @@
     </row>
     <row r="69" spans="1:20">
       <c r="A69" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>49</v>
@@ -5551,16 +5551,16 @@
         <v>28</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J69" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M69" s="5" t="s">
         <v>28</v>
@@ -5569,16 +5569,16 @@
         <v>28</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P69" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q69" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R69" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S69" s="5" t="s">
         <v>30</v>
@@ -5589,16 +5589,16 @@
     </row>
     <row r="70" spans="1:20">
       <c r="A70" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E70" s="5" t="s">
         <v>26</v>
@@ -5613,16 +5613,16 @@
         <v>28</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J70" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M70" s="5" t="s">
         <v>28</v>
@@ -5631,16 +5631,16 @@
         <v>28</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P70" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q70" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R70" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S70" s="5" t="s">
         <v>30</v>
@@ -5651,10 +5651,10 @@
     </row>
     <row r="71" spans="1:20">
       <c r="A71" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>49</v>
@@ -5675,16 +5675,16 @@
         <v>29</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J71" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M71" s="5" t="s">
         <v>28</v>
@@ -5693,16 +5693,16 @@
         <v>28</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P71" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q71" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R71" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S71" s="6" t="s">
         <v>35</v>
@@ -5713,10 +5713,10 @@
     </row>
     <row r="72" spans="1:20">
       <c r="A72" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>49</v>
@@ -5737,16 +5737,16 @@
         <v>29</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J72" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M72" s="4" t="s">
         <v>29</v>
@@ -5755,16 +5755,16 @@
         <v>29</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P72" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q72" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R72" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S72" s="5" t="s">
         <v>30</v>
@@ -5775,10 +5775,10 @@
     </row>
     <row r="73" spans="1:20">
       <c r="A73" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C73" s="4" t="s">
         <v>49</v>
@@ -5799,16 +5799,16 @@
         <v>29</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J73" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M73" s="4" t="s">
         <v>29</v>
@@ -5817,16 +5817,16 @@
         <v>29</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P73" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q73" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R73" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S73" s="5" t="s">
         <v>30</v>
@@ -5837,16 +5837,16 @@
     </row>
     <row r="74" spans="1:20">
       <c r="A74" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E74" s="5" t="s">
         <v>26</v>
@@ -5861,16 +5861,16 @@
         <v>28</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J74" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M74" s="5" t="s">
         <v>28</v>
@@ -5879,16 +5879,16 @@
         <v>28</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P74" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q74" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R74" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S74" s="5" t="s">
         <v>30</v>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="75" spans="1:20">
       <c r="A75" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>49</v>
@@ -5923,16 +5923,16 @@
         <v>29</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J75" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M75" s="5" t="s">
         <v>28</v>
@@ -5941,16 +5941,16 @@
         <v>29</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P75" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q75" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R75" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S75" s="5" t="s">
         <v>30</v>
@@ -5961,16 +5961,16 @@
     </row>
     <row r="76" spans="1:20">
       <c r="A76" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>34</v>
@@ -5985,16 +5985,16 @@
         <v>29</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J76" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M76" s="4" t="s">
         <v>29</v>
@@ -6003,16 +6003,16 @@
         <v>28</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P76" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q76" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R76" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S76" s="6" t="s">
         <v>35</v>
@@ -6023,16 +6023,16 @@
     </row>
     <row r="77" spans="1:20">
       <c r="A77" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>34</v>
@@ -6047,16 +6047,16 @@
         <v>29</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J77" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M77" s="4" t="s">
         <v>29</v>
@@ -6065,16 +6065,16 @@
         <v>28</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P77" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q77" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R77" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S77" s="6" t="s">
         <v>35</v>
@@ -6085,16 +6085,16 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C78" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>34</v>
@@ -6109,16 +6109,16 @@
         <v>29</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J78" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M78" s="4" t="s">
         <v>29</v>
@@ -6127,16 +6127,16 @@
         <v>28</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P78" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q78" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R78" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S78" s="6" t="s">
         <v>35</v>
@@ -6147,13 +6147,13 @@
     </row>
     <row r="79" spans="1:20">
       <c r="A79" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>193</v>
+        <v>32</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>194</v>
@@ -6171,16 +6171,16 @@
         <v>29</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J79" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M79" s="4" t="s">
         <v>29</v>
@@ -6189,16 +6189,16 @@
         <v>28</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P79" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q79" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R79" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S79" s="6" t="s">
         <v>35</v>
@@ -6233,16 +6233,16 @@
         <v>29</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J80" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M80" s="4" t="s">
         <v>29</v>
@@ -6251,16 +6251,16 @@
         <v>28</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P80" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q80" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R80" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S80" s="6" t="s">
         <v>35</v>
@@ -6277,7 +6277,7 @@
         <v>198</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>88</v>
@@ -6295,16 +6295,16 @@
         <v>29</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J81" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M81" s="4" t="s">
         <v>29</v>
@@ -6313,16 +6313,16 @@
         <v>29</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P81" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q81" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R81" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S81" s="5" t="s">
         <v>30</v>
@@ -6339,7 +6339,7 @@
         <v>200</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>88</v>
@@ -6357,16 +6357,16 @@
         <v>29</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J82" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M82" s="4" t="s">
         <v>29</v>
@@ -6375,16 +6375,16 @@
         <v>29</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P82" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q82" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R82" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S82" s="5" t="s">
         <v>30</v>
@@ -6401,7 +6401,7 @@
         <v>202</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>88</v>
@@ -6419,16 +6419,16 @@
         <v>29</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J83" s="4" t="s">
         <v>28</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M83" s="4" t="s">
         <v>29</v>
@@ -6437,22 +6437,22 @@
         <v>29</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P83" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q83" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R83" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S83" s="6" t="s">
         <v>35</v>
       </c>
       <c r="T83" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="84" spans="1:20">
@@ -6463,7 +6463,7 @@
         <v>204</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D84" s="4" t="s">
         <v>88</v>
@@ -6481,16 +6481,16 @@
         <v>29</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J84" s="4" t="s">
         <v>28</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M84" s="4" t="s">
         <v>29</v>
@@ -6499,22 +6499,22 @@
         <v>29</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P84" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q84" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R84" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S84" s="6" t="s">
         <v>35</v>
       </c>
       <c r="T84" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="85" spans="1:20">
@@ -6522,10 +6522,10 @@
         <v>205</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D85" s="4" t="s">
         <v>72</v>
@@ -6543,16 +6543,16 @@
         <v>29</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J85" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M85" s="4" t="s">
         <v>29</v>
@@ -6561,16 +6561,16 @@
         <v>28</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P85" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q85" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R85" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S85" s="6" t="s">
         <v>35</v>
@@ -6587,10 +6587,10 @@
         <v>207</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>34</v>
@@ -6605,40 +6605,40 @@
         <v>29</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J86" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M86" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="N86" s="4" t="s">
-        <v>29</v>
+      <c r="N86" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P86" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q86" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R86" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="S86" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="T86" s="7" t="s">
-        <v>68</v>
+        <v>68</v>
+      </c>
+      <c r="S86" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="T86" s="6" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="87" spans="1:20">
@@ -6649,10 +6649,10 @@
         <v>209</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>67</v>
+        <v>187</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>34</v>
@@ -6667,40 +6667,40 @@
         <v>29</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J87" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M87" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="N87" s="4" t="s">
-        <v>29</v>
+      <c r="N87" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P87" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q87" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R87" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="S87" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="T87" s="7" t="s">
-        <v>68</v>
+        <v>68</v>
+      </c>
+      <c r="S87" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="T87" s="6" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="88" spans="1:20">
@@ -6711,10 +6711,10 @@
         <v>211</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>34</v>
@@ -6729,16 +6729,16 @@
         <v>29</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J88" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M88" s="4" t="s">
         <v>29</v>
@@ -6747,16 +6747,16 @@
         <v>28</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P88" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q88" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R88" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S88" s="6" t="s">
         <v>35</v>
@@ -6773,10 +6773,10 @@
         <v>213</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>34</v>
@@ -6791,16 +6791,16 @@
         <v>29</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J89" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M89" s="4" t="s">
         <v>29</v>
@@ -6809,16 +6809,16 @@
         <v>28</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P89" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q89" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R89" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S89" s="6" t="s">
         <v>35</v>
@@ -6835,10 +6835,10 @@
         <v>215</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>34</v>
@@ -6853,16 +6853,16 @@
         <v>29</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J90" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M90" s="4" t="s">
         <v>29</v>
@@ -6871,16 +6871,16 @@
         <v>28</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P90" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q90" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R90" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S90" s="6" t="s">
         <v>35</v>
@@ -6897,10 +6897,10 @@
         <v>217</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>34</v>
@@ -6915,16 +6915,16 @@
         <v>29</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J91" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M91" s="4" t="s">
         <v>29</v>
@@ -6933,22 +6933,22 @@
         <v>29</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P91" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q91" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R91" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S91" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T91" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="92" spans="1:20">
@@ -6959,10 +6959,10 @@
         <v>219</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E92" s="5" t="s">
         <v>26</v>
@@ -6977,16 +6977,16 @@
         <v>28</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J92" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M92" s="5" t="s">
         <v>28</v>
@@ -6995,16 +6995,16 @@
         <v>28</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P92" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q92" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R92" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S92" s="5" t="s">
         <v>30</v>
@@ -7021,10 +7021,10 @@
         <v>221</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E93" s="5" t="s">
         <v>26</v>
@@ -7039,16 +7039,16 @@
         <v>28</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J93" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M93" s="4" t="s">
         <v>29</v>
@@ -7057,22 +7057,22 @@
         <v>29</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P93" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q93" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R93" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S93" s="7" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="T93" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="94" spans="1:20">
@@ -7083,7 +7083,7 @@
         <v>223</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D94" s="4" t="s">
         <v>224</v>
@@ -7101,16 +7101,16 @@
         <v>28</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J94" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M94" s="5" t="s">
         <v>28</v>
@@ -7119,16 +7119,16 @@
         <v>28</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P94" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q94" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R94" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S94" s="5" t="s">
         <v>30</v>
@@ -7145,7 +7145,7 @@
         <v>226</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>72</v>
@@ -7163,16 +7163,16 @@
         <v>29</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J95" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M95" s="4" t="s">
         <v>29</v>
@@ -7181,16 +7181,16 @@
         <v>28</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P95" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q95" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R95" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S95" s="6" t="s">
         <v>35</v>
@@ -7225,16 +7225,16 @@
         <v>29</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J96" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M96" s="4" t="s">
         <v>29</v>
@@ -7243,16 +7243,16 @@
         <v>28</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P96" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q96" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R96" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S96" s="6" t="s">
         <v>35</v>
@@ -7269,10 +7269,10 @@
         <v>229</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E97" s="4" t="s">
         <v>34</v>
@@ -7287,16 +7287,16 @@
         <v>29</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J97" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M97" s="4" t="s">
         <v>29</v>
@@ -7305,22 +7305,22 @@
         <v>29</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P97" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q97" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R97" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S97" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T97" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="98" spans="1:20">
@@ -7331,10 +7331,10 @@
         <v>231</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E98" s="5" t="s">
         <v>26</v>
@@ -7349,16 +7349,16 @@
         <v>28</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J98" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M98" s="4" t="s">
         <v>29</v>
@@ -7367,22 +7367,22 @@
         <v>29</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P98" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q98" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R98" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S98" s="7" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="T98" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="99" spans="1:20">
@@ -7393,10 +7393,10 @@
         <v>233</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E99" s="5" t="s">
         <v>26</v>
@@ -7411,16 +7411,16 @@
         <v>28</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J99" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M99" s="4" t="s">
         <v>29</v>
@@ -7429,22 +7429,22 @@
         <v>29</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P99" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q99" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R99" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S99" s="7" t="s">
-        <v>96</v>
+        <v>127</v>
       </c>
       <c r="T99" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -7452,7 +7452,7 @@
         <v>234</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>49</v>
@@ -7473,16 +7473,16 @@
         <v>29</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J100" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M100" s="4" t="s">
         <v>29</v>
@@ -7491,16 +7491,16 @@
         <v>29</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P100" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q100" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R100" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S100" s="6" t="s">
         <v>35</v>
@@ -7514,10 +7514,10 @@
         <v>235</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D101" s="4" t="s">
         <v>72</v>
@@ -7535,16 +7535,16 @@
         <v>29</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J101" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M101" s="4" t="s">
         <v>29</v>
@@ -7553,16 +7553,16 @@
         <v>28</v>
       </c>
       <c r="O101" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P101" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q101" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R101" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S101" s="6" t="s">
         <v>35</v>
@@ -7579,10 +7579,10 @@
         <v>237</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E102" s="4" t="s">
         <v>34</v>
@@ -7597,16 +7597,16 @@
         <v>29</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J102" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M102" s="4" t="s">
         <v>29</v>
@@ -7615,16 +7615,16 @@
         <v>28</v>
       </c>
       <c r="O102" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P102" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q102" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R102" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S102" s="6" t="s">
         <v>35</v>
@@ -7641,10 +7641,10 @@
         <v>239</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E103" s="4" t="s">
         <v>34</v>
@@ -7659,16 +7659,16 @@
         <v>29</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J103" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M103" s="4" t="s">
         <v>29</v>
@@ -7677,16 +7677,16 @@
         <v>28</v>
       </c>
       <c r="O103" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P103" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q103" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R103" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S103" s="6" t="s">
         <v>35</v>
@@ -7700,10 +7700,10 @@
         <v>240</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>72</v>
@@ -7721,16 +7721,16 @@
         <v>28</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J104" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M104" s="5" t="s">
         <v>28</v>
@@ -7739,16 +7739,16 @@
         <v>28</v>
       </c>
       <c r="O104" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P104" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q104" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R104" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S104" s="5" t="s">
         <v>30</v>
@@ -7765,10 +7765,10 @@
         <v>223</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E105" s="4" t="s">
         <v>34</v>
@@ -7783,16 +7783,16 @@
         <v>29</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J105" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M105" s="4" t="s">
         <v>29</v>
@@ -7801,22 +7801,22 @@
         <v>29</v>
       </c>
       <c r="O105" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P105" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q105" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R105" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S105" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T105" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="106" spans="1:20">
@@ -7827,10 +7827,10 @@
         <v>243</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E106" s="4" t="s">
         <v>34</v>
@@ -7845,16 +7845,16 @@
         <v>29</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J106" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M106" s="4" t="s">
         <v>29</v>
@@ -7863,22 +7863,22 @@
         <v>29</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P106" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q106" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R106" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S106" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T106" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="107" spans="1:20">
@@ -7889,10 +7889,10 @@
         <v>245</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E107" s="4" t="s">
         <v>34</v>
@@ -7907,16 +7907,16 @@
         <v>29</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J107" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M107" s="4" t="s">
         <v>29</v>
@@ -7925,22 +7925,22 @@
         <v>29</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P107" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q107" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R107" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S107" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T107" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="108" spans="1:20">
@@ -7951,10 +7951,10 @@
         <v>247</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E108" s="4" t="s">
         <v>34</v>
@@ -7969,16 +7969,16 @@
         <v>29</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J108" s="4" t="s">
         <v>28</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M108" s="4" t="s">
         <v>29</v>
@@ -7987,22 +7987,22 @@
         <v>29</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P108" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q108" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R108" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S108" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T108" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="109" spans="1:20">
@@ -8013,10 +8013,10 @@
         <v>249</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E109" s="4" t="s">
         <v>34</v>
@@ -8031,16 +8031,16 @@
         <v>29</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J109" s="4" t="s">
         <v>28</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M109" s="4" t="s">
         <v>29</v>
@@ -8049,22 +8049,22 @@
         <v>29</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P109" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q109" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R109" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S109" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T109" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="110" spans="1:20">
@@ -8447,7 +8447,7 @@
         <v>263</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D116" s="4" t="s">
         <v>72</v>
@@ -8509,7 +8509,7 @@
         <v>265</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D117" s="4" t="s">
         <v>75</v>
@@ -8633,7 +8633,7 @@
         <v>265</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="D119" s="4" t="s">
         <v>75</v>
@@ -8698,7 +8698,7 @@
         <v>49</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E120" s="5" t="s">
         <v>26</v>
@@ -8757,10 +8757,10 @@
         <v>272</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E121" s="4" t="s">
         <v>34</v>
@@ -8775,16 +8775,16 @@
         <v>29</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J121" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>29</v>
@@ -8793,22 +8793,22 @@
         <v>29</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P121" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q121" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R121" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S121" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T121" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="122" spans="1:20">
@@ -8819,10 +8819,10 @@
         <v>274</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E122" s="4" t="s">
         <v>34</v>
@@ -8881,10 +8881,10 @@
         <v>276</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E123" s="4" t="s">
         <v>34</v>
@@ -8899,16 +8899,16 @@
         <v>29</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J123" s="4" t="s">
         <v>29</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M123" s="4" t="s">
         <v>29</v>
@@ -8917,16 +8917,16 @@
         <v>28</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P123" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q123" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R123" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S123" s="6" t="s">
         <v>35</v>
@@ -8946,7 +8946,7 @@
         <v>49</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>34</v>
@@ -9008,7 +9008,7 @@
         <v>49</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E125" s="4" t="s">
         <v>34</v>
@@ -9070,7 +9070,7 @@
         <v>32</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E126" s="4" t="s">
         <v>34</v>
@@ -9132,7 +9132,7 @@
         <v>32</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E127" s="4" t="s">
         <v>34</v>
@@ -9194,7 +9194,7 @@
         <v>32</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E128" s="4" t="s">
         <v>34</v>
@@ -9256,7 +9256,7 @@
         <v>32</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>34</v>
@@ -9318,7 +9318,7 @@
         <v>32</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E130" s="4" t="s">
         <v>34</v>
@@ -9395,16 +9395,16 @@
         <v>29</v>
       </c>
       <c r="I131" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J131" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K131" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L131" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M131" s="5" t="s">
         <v>28</v>
@@ -9413,16 +9413,16 @@
         <v>29</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P131" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q131" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R131" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S131" s="5" t="s">
         <v>30</v>
@@ -9439,7 +9439,7 @@
         <v>289</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D132" s="4" t="s">
         <v>47</v>
@@ -9457,16 +9457,16 @@
         <v>29</v>
       </c>
       <c r="I132" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J132" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K132" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L132" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M132" s="4" t="s">
         <v>29</v>
@@ -9475,16 +9475,16 @@
         <v>28</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P132" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q132" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R132" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S132" s="6" t="s">
         <v>35</v>
@@ -9501,10 +9501,10 @@
         <v>292</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E133" s="4" t="s">
         <v>34</v>
@@ -9519,16 +9519,16 @@
         <v>29</v>
       </c>
       <c r="I133" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J133" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K133" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L133" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M133" s="4" t="s">
         <v>29</v>
@@ -9537,22 +9537,22 @@
         <v>29</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P133" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q133" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R133" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S133" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T133" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="134" spans="1:20">
@@ -9563,10 +9563,10 @@
         <v>294</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>34</v>
@@ -9581,16 +9581,16 @@
         <v>29</v>
       </c>
       <c r="I134" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J134" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K134" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L134" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M134" s="4" t="s">
         <v>29</v>
@@ -9599,22 +9599,22 @@
         <v>29</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P134" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q134" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R134" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S134" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T134" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="135" spans="1:20">
@@ -9625,10 +9625,10 @@
         <v>296</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E135" s="4" t="s">
         <v>34</v>
@@ -9643,16 +9643,16 @@
         <v>29</v>
       </c>
       <c r="I135" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J135" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K135" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L135" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M135" s="4" t="s">
         <v>29</v>
@@ -9661,22 +9661,22 @@
         <v>29</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P135" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q135" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R135" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S135" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T135" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="136" spans="1:20">
@@ -9687,10 +9687,10 @@
         <v>298</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E136" s="4" t="s">
         <v>34</v>
@@ -9705,16 +9705,16 @@
         <v>29</v>
       </c>
       <c r="I136" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J136" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K136" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L136" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M136" s="4" t="s">
         <v>29</v>
@@ -9723,22 +9723,22 @@
         <v>29</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P136" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q136" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R136" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S136" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T136" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="137" spans="1:20">
@@ -9749,10 +9749,10 @@
         <v>300</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E137" s="4" t="s">
         <v>34</v>
@@ -9767,16 +9767,16 @@
         <v>29</v>
       </c>
       <c r="I137" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J137" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K137" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L137" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M137" s="4" t="s">
         <v>29</v>
@@ -9785,22 +9785,22 @@
         <v>29</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P137" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q137" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R137" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S137" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T137" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="138" spans="1:20">
@@ -9811,10 +9811,10 @@
         <v>292</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E138" s="4" t="s">
         <v>34</v>
@@ -9829,16 +9829,16 @@
         <v>29</v>
       </c>
       <c r="I138" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J138" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K138" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L138" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M138" s="4" t="s">
         <v>29</v>
@@ -9847,22 +9847,22 @@
         <v>29</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P138" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q138" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R138" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S138" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T138" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="139" spans="1:20">
@@ -9873,10 +9873,10 @@
         <v>294</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>34</v>
@@ -9891,16 +9891,16 @@
         <v>29</v>
       </c>
       <c r="I139" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J139" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K139" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L139" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M139" s="4" t="s">
         <v>29</v>
@@ -9909,22 +9909,22 @@
         <v>29</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P139" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q139" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R139" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S139" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T139" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="140" spans="1:20">
@@ -9935,10 +9935,10 @@
         <v>296</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="E140" s="4" t="s">
         <v>34</v>
@@ -9953,16 +9953,16 @@
         <v>29</v>
       </c>
       <c r="I140" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J140" s="4" t="s">
         <v>34</v>
       </c>
       <c r="K140" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L140" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M140" s="4" t="s">
         <v>29</v>
@@ -9971,22 +9971,22 @@
         <v>29</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P140" s="4" t="s">
         <v>29</v>
       </c>
       <c r="Q140" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R140" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S140" s="5" t="s">
         <v>30</v>
       </c>
       <c r="T140" s="7" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>
@@ -10032,13 +10032,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C2" s="6">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D2" s="7">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="E2" s="4">
         <v>1</v>
